--- a/docs/培训/OpenWorker培训/03-设备点检/设备台账.xlsx
+++ b/docs/培训/OpenWorker培训/03-设备点检/设备台账.xlsx
@@ -507,10 +507,10 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -545,10 +545,10 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -773,10 +773,10 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46287</v>
+        <v>46292</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46287</v>
+        <v>46292</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46299</v>
+        <v>46304</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>46264</v>
+        <v>46269</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>46282</v>
+        <v>46287</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46312</v>
+        <v>46317</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
